--- a/data/trans_camb/P59A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,53</t>
+          <t>-0,94; 8,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,25</t>
+          <t>-2,86; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 8,23</t>
+          <t>-2,31; 8,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,31</t>
+          <t>-0,66; 5,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 4,2</t>
+          <t>-1,88; 4,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,02</t>
+          <t>-1,98; 3,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,58</t>
+          <t>0,13; 5,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,87</t>
+          <t>-1,22; 4,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,28</t>
+          <t>-1,27; 4,21</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 149,15</t>
+          <t>-11,29; 145,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 108,91</t>
+          <t>-31,43; 104,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 133,96</t>
+          <t>-27,89; 148,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 153,43</t>
+          <t>-15,23; 155,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 124,39</t>
+          <t>-33,59; 130,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,89; 121,43</t>
+          <t>-35,54; 113,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 120,68</t>
+          <t>1,87; 116,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 78,06</t>
+          <t>-18,2; 85,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 91,98</t>
+          <t>-18,15; 90,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 4,98</t>
+          <t>-2,43; 5,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,17</t>
+          <t>0,28; 7,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 5,67</t>
+          <t>-2,45; 5,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 9,21</t>
+          <t>1,16; 9,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,03</t>
+          <t>1,04; 8,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 5,38</t>
+          <t>-2,22; 5,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,65</t>
+          <t>0,41; 5,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,92</t>
+          <t>1,92; 7,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,54</t>
+          <t>-1,12; 4,48</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 39,39</t>
+          <t>-15,06; 45,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 64,31</t>
+          <t>1,48; 62,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 44,42</t>
+          <t>-15,2; 45,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 87,6</t>
+          <t>7,84; 93,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 80,44</t>
+          <t>7,34; 78,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 52,03</t>
+          <t>-15,92; 51,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 46,46</t>
+          <t>2,74; 45,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 58,21</t>
+          <t>12,15; 59,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 37,4</t>
+          <t>-8,09; 37,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 8,8</t>
+          <t>-7,46; 8,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 10,63</t>
+          <t>-3,99; 10,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 7,53</t>
+          <t>-6,97; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 12,81</t>
+          <t>-4,53; 12,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,31</t>
+          <t>-6,66; 7,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 9,23</t>
+          <t>-3,89; 9,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 8,56</t>
+          <t>-3,7; 8,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 6,87</t>
+          <t>-4,09; 6,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,62</t>
+          <t>-3,73; 5,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 54,48</t>
+          <t>-32,48; 52,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 68,6</t>
+          <t>-19,19; 67,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 49,43</t>
+          <t>-31,57; 53,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 95,87</t>
+          <t>-23,61; 88,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 47,96</t>
+          <t>-31,94; 60,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 71,73</t>
+          <t>-19,12; 69,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 53,43</t>
+          <t>-17,75; 53,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 44,89</t>
+          <t>-19,46; 42,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 42,42</t>
+          <t>-17,84; 37,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,48</t>
+          <t>-1,25; 4,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,6</t>
+          <t>0,81; 6,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,35</t>
+          <t>-0,71; 4,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,83</t>
+          <t>1,51; 6,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,26</t>
+          <t>1,58; 6,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,48</t>
+          <t>0,32; 5,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,74</t>
+          <t>0,85; 4,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,6</t>
+          <t>2,12; 5,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,41</t>
+          <t>0,49; 4,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 36,17</t>
+          <t>-8,14; 35,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 54,51</t>
+          <t>4,75; 52,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 44,27</t>
+          <t>-4,43; 40,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,19; 74,85</t>
+          <t>13,08; 75,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 69,82</t>
+          <t>13,06; 68,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 61,41</t>
+          <t>2,68; 61,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 42,48</t>
+          <t>6,84; 43,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,64; 51,02</t>
+          <t>16,33; 52,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 40,07</t>
+          <t>3,62; 40,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P59A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,24</t>
+          <t>-0,82; 8,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 6,2</t>
+          <t>-3,08; 5,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,44</t>
+          <t>-3,24; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,38</t>
+          <t>-0,72; 5,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,4</t>
+          <t>-1,7; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,87</t>
+          <t>-2,11; 3,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,53</t>
+          <t>0,19; 5,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,0</t>
+          <t>-1,16; 3,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,21</t>
+          <t>-1,51; 3,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 145,52</t>
+          <t>-12,93; 144,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,43; 104,04</t>
+          <t>-34,21; 100,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 148,59</t>
+          <t>-34,56; 112,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 155,24</t>
+          <t>-16,1; 151,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 130,52</t>
+          <t>-30,57; 123,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 113,62</t>
+          <t>-36,96; 105,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 116,77</t>
+          <t>3,48; 115,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 85,02</t>
+          <t>-16,96; 78,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 90,37</t>
+          <t>-23,01; 79,11</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>2,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 5,44</t>
+          <t>-2,29; 5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,99</t>
+          <t>0,36; 8,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,68</t>
+          <t>-1,57; 6,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,33</t>
+          <t>1,63; 8,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,05</t>
+          <t>1,01; 7,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 5,37</t>
+          <t>-0,7; 6,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,56</t>
+          <t>0,45; 5,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,06</t>
+          <t>1,54; 6,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,48</t>
+          <t>0,06; 5,39</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 45,62</t>
+          <t>-14,16; 41,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 62,87</t>
+          <t>2,26; 68,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 45,59</t>
+          <t>-9,52; 52,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,84; 93,45</t>
+          <t>12,07; 88,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 78,33</t>
+          <t>7,64; 81,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 51,77</t>
+          <t>-5,09; 62,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 45,89</t>
+          <t>2,94; 47,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 59,67</t>
+          <t>11,14; 57,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 37,15</t>
+          <t>0,2; 44,36</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 8,49</t>
+          <t>-7,27; 8,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 10,32</t>
+          <t>-4,9; 10,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 7,4</t>
+          <t>-7,13; 7,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 12,06</t>
+          <t>-3,53; 12,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 7,49</t>
+          <t>-7,0; 7,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 9,33</t>
+          <t>-4,37; 8,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 8,02</t>
+          <t>-3,2; 8,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 6,45</t>
+          <t>-3,78; 6,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 5,96</t>
+          <t>-3,32; 6,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 52,92</t>
+          <t>-31,32; 53,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 67,14</t>
+          <t>-22,88; 70,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 53,55</t>
+          <t>-32,79; 44,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 88,09</t>
+          <t>-18,18; 92,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 60,52</t>
+          <t>-33,41; 54,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 69,04</t>
+          <t>-21,01; 65,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 53,3</t>
+          <t>-15,68; 51,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 42,27</t>
+          <t>-18,07; 40,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 37,86</t>
+          <t>-15,45; 44,67</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>3,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,34</t>
+          <t>-1,05; 4,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,57</t>
+          <t>0,94; 6,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,95</t>
+          <t>-0,16; 5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,78</t>
+          <t>1,45; 6,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,31</t>
+          <t>1,68; 6,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,5</t>
+          <t>1,31; 5,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,74</t>
+          <t>1,02; 4,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,81</t>
+          <t>1,85; 5,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,54</t>
+          <t>1,32; 4,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 35,34</t>
+          <t>-7,7; 38,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 52,68</t>
+          <t>6,22; 54,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 40,49</t>
+          <t>-0,95; 47,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 75,41</t>
+          <t>12,28; 73,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 68,26</t>
+          <t>13,76; 73,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 61,35</t>
+          <t>11,14; 65,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 43,64</t>
+          <t>7,82; 44,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,33; 52,51</t>
+          <t>14,16; 52,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 40,66</t>
+          <t>10,09; 45,01</t>
         </is>
       </c>
     </row>
